--- a/public/converted/scheta-ot-19-10-26-v-zagruzku.xlsx
+++ b/public/converted/scheta-ot-19-10-26-v-zagruzku.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$3:$H$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$3:$H$415</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Счета № 1222 и № 1223 от 20.10.2026, ООО "ВГ-ТРЕЙД"</t>
+          <t>Счета № 1222 и № 1223 от 20.10.2026, № 1202 от 15.10.2026, ООО "ВГ-ТРЕЙД"</t>
         </is>
       </c>
     </row>
@@ -5409,8 +5409,4562 @@
         <v>36221.5</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>441219</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>4393720609704</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Водонагреватель накопительный Weissgauff WWH 10 Comfort UR</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>424922</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>4393720452591</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Aura 1200 Remote WH</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>442215</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>4640213440338</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Aura 452 Touch White Glass</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>435999</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>4393720602422</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Aura 456 PB Black Glass</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>436000</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>4393720602439</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Aura 456 Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>424919</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>4393720452560</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Aura 850 BL</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>436096</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>4393720602446</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 1000 BL Sensor</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>429195</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>4393720465515</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 1200 BL</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>429196</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>4393720465522</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 1200 WH</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E226" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>433584</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>4393720600602</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 40 PB Black</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>433585</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>4393720600619</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 40 PB White</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="5" t="n">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>439043</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>4393720605966</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 450 PB BL</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>430311</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>4393720470533</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 452 White</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>439044</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>4393720605973</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 520 PB BL</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>439254</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>4393720606932</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 600 Black Edition</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>435135</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>4393720601753</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 600 PB BL</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E233" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>435137</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>4393720601722</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 600 PB IX</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>435136</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>4393720601760</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 600 PB WH</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E235" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>439255</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>4393720606949</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 600 White</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E236" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>436113</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>4393720602453</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 850 PB Black Edition</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E237" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>438794</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>4393720605607</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 900 PB IX</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>439258</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>4393720606963</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 50 Black</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E239" s="5" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>439259</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>4393720606970</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 50 White</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E240" s="5" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>439209</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>4393720606574</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 500 White</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E241" s="5" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>439260</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>4393720606987</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 60 Black</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E242" s="5" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>439261</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>4393720606994</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 60 White</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E243" s="5" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>439048</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>4393720606017</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 600 Black</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E244" s="5" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>439049</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>4393720606024</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Cover 600 White</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E245" s="5" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>439290</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>4393720606789</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Dubhe 450 Black Edition</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E246" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>439294</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>4393720606802</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Dubhe 450 White</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E247" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>433182</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>4393720478225</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Dubhe 600 Black Touch</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>433179</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>4393720478218</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff FIONA 60 BL</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E249" s="5" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>439045</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>4393720605980</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Integra 850 PB BL</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E250" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>439047</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>4393720606000</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Integra 850 PB IX</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E251" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>439046</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>4393720605997</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Integra 850 PB WH</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E252" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>430367</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>4393720470274</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Intense 600 Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>430910</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>4393720472643</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Merga 60 BL Sensor</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>439042</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>4393720605959</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Quadra 600 Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>430135</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>4393720469568</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff SIGMA 50 PB BL</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>430136</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>4393720469575</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff SIGMA 50 PB WH</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>356151</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>4393720467588</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff SIGMA 60 PB BL</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>356150</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>4393720467595</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff SIGMA 60 PB WH</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="5" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>439264</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>4393720606635</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 06 1M BM</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>418251</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>4393720447030</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 06 1M IX</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>439265</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>4393720606642</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 06 1M WM</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E262" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>418250</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>4393720447023</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 06 2M IX</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E263" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>438285</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>4393720604563</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 450 Black Glass</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E264" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>438287</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>4393720604570</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 450 Inox</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>438286</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>4393720604587</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 450 White Glass</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>438277</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>4393720604594</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 500 Black Glass</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>438278</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>4393720604600</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 500 White Glass</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>438282</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>4393720604624</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 2M Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>438283</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>4393720604631</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 2M Touch White Glass</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E270" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>436620</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>4393720602804</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 Black Glass</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>436624</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>4393720602828</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 TC BL</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E272" s="5" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>436625</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>4393720602835</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 TC WH</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>436623</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>4393720602811</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 600 White Glass</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="5" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>438290</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>4393720604679</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Yota 600 Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>438291</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>4393720604686</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Yota 600 Touch White Glass</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>431736</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>4393720474951</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zaurak 50 PB WH</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>430906</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>4393720472605</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zaurak 60 PB BL</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>430907</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>4393720472612</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zaurak 60 PB WH</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>431733</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>4393720474920</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zosma 50 PB BL</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>430899</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>4393720472537</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zosma 50 PB WH</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>431734</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>4393720474937</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zosma 60 PB BL</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E282" s="5" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>430902</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>4393720472568</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zosma 60 PB IX</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>430901</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>4393720472551</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Zosma 60 PB WH</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>433207</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>4393720600091</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 430 WGV</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>440036</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>4393720608738</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 451 BFh</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" s="5" t="n">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>433582</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>4393720600572</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 640 WGh</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>411841</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>4393720445432</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BGh</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" s="5" t="n">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>411843</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>4393720445456</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 Xh</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>436188</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>4393720602743</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 6441 BG Brass</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" s="5" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>442220</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>4670239260344</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 741 BFH</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>439050</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>4393720605898</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 104 B</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E292" s="5" t="n">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>431442</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>4393720473633</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 262 PMW</t>
+        </is>
+      </c>
+      <c r="D293" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>267969</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>4670239261051</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Измельчитель пищевых отходов Weissgauff ISE 860</t>
+        </is>
+      </c>
+      <c r="D294" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>433103</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>4393720477938</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Кофемашина Weissgauff WCMI-576 Touch Cappuccino</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>13499</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>437402</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>4393720603573</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff BMWO-206</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>437427</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>4393720603559</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-2016 BGL</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>432977</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>4393720477860</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4026</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E298" s="5" t="n">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>432984</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>4393720478003</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4525 Infolight</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>426062</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>4393720458937</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4533 D</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E300" s="5" t="n">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>431381</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>4393720473350</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4536 D Infolight</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>433987</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>4393720600695</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4536 D Inverter AutoOpen Infolight</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>429861</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>4393720468332</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4537</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>438943</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>4393720605652</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4538 Touch Inverter Autoopen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E304" s="5" t="n">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>442675</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>4670239260856</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4539 Touch Inverter Autoopen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E305" s="5" t="n">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>432188</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>4393720475972</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4575 D Inverter AutoOpen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" s="5" t="n">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>432987</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>4393720478010</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6025 D Infolight</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E307" s="5" t="n">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>432982</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>4393720477914</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6036 D AutoOpen</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" s="5" t="n">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>431378</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>4393720473343</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6036 D Infolight</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>429864</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>4393720468363</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6037</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>434465</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>4393720601197</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6037 Inverter AutoOpen Infolight</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>433534</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>4393720600589</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6038 D Autoopen</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>433535</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>4393720600596</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6038 D Inverter Autoopen</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E313" s="5" t="n">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>437354</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>4393720603498</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6038 Infolight</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>426065</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>4393720458968</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6073 D</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" s="5" t="n">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>438945</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>4393720605669</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6138 Touch Inverter Autoopen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E316" s="5" t="n">
+        <v>4949</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>432194</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>4393720476047</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6151 Inverter Touch AutoOpen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E317" s="5" t="n">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>432176</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>4393720475927</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 4539 Inverter Touch AutoOpen Black</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" s="5" t="n">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>437357</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>4393720603443</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 6038 Autoopen</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" s="5" t="n">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>437360</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>4393720603962</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 6038 X Inverter</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E320" s="5" t="n">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>437882</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>4393720604174</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 799 Touch Autoopen</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" s="5" t="n">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>419427</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>4393720447900</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4006</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E322" s="5" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>419432</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>4393720447917</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4017 D</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" s="5" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>424447</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>4393720450955</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4017 DS</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E324" s="5" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>429211</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>4393720465997</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4036 D</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E325" s="5" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>426645</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>4393720462897</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4037 D</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E326" s="5" t="n">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>430212</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>4393720470328</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4106 Led</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E327" s="5" t="n">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>431075</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>4393720471882</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Смеситель Weissgauff WG 01602 Beige</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E328" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>441313</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>4610249316419</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Смеситель Weissgauff WG 016328 Comfort Beige Sand</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E329" s="5" t="n">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>441319</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>4610249316464</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Смеситель Weissgauff WG 019344 Comfort Deep Space</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E330" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>432635</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>4610117753865</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Соединительный элемент Weissgauff WCE 14300</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E331" s="5" t="n">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>434831</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>4393720601319</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Соединительный элемент Weissgauff WSK 30300 Champagne</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E332" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>412021</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>4393720445531</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E333" s="5" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>430966</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>4393720472889</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32 BA</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E334" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>439168</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>4393720606918</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32 BA Flex</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E335" s="5" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>427769</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>4393720464167</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32 BFZC</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E336" s="5" t="n">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>433413</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>4393720600428</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32 WA</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>427771</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>4393720464174</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 32 WFZC</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E338" s="5" t="n">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>427772</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>4393720464150</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 412 H</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E339" s="5" t="n">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>436892</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>4393720602972</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 430 BM</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E340" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>436893</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>4393720602989</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 430 BM Flex Zone</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E341" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>430968</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>4393720472902</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 640 BA</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E342" s="5" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>423433</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>4393720450795</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 640 BSC</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E343" s="5" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>434270</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>4393720601043</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 642 BFZG</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E344" s="5" t="n">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>431341</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>4393720473220</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 642 BSCM</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E345" s="5" t="n">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>437506</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>4393720603795</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 642 GFZG</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>425379</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>4393720458623</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 643 BFZC</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>434269</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>4393720601036</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HI 643 BFZG</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>439182</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>4393720606901</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 312 BKS</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E349" s="5" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>440163</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>4393720608844</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 32 BAT</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E350" s="5" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>435692</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>4393720602194</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 32 BKS</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E351" s="5" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>431362</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>4393720473268</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 32 BM</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" s="5" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>420920</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>4393720450597</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 430 BS</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E353" s="5" t="n">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>418840</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>4393720447115</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 431 B</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>433480</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>4393720600466</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 633 BS</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" s="5" t="n">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>441912</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>4670239260030</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 640 BAT</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E356" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>410085</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>4393720445005</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 640 BK</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" s="5" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>435693</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>4393720602200</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 640 BKS</t>
+        </is>
+      </c>
+      <c r="D358" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E358" s="5" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>410084</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>4393720444992</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 640 BS</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E359" s="5" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>410086</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>4393720470342</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 641 BS</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" s="5" t="n">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>431344</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>4393720473251</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 642 BM</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E361" s="5" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>410089</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>4393720470366</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Стеклокерамическая панель Weissgauff HV 643 BS</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E362" s="5" t="n">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>440451</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>4393720609094</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 39107 Full Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" s="5" t="n">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>439783</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>4393720608394</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 39107 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" s="5" t="n">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>438789</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>4393720605782</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 40106 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E365" s="5" t="n">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>431741</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>4393720474913</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 40165 T</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E366" s="5" t="n">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>426826</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>4393720463795</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4106 D</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" s="5" t="n">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>439111</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>4393720606260</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4106 D Deep Grey</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E368" s="5" t="n">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>438965</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>4393720605676</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 41106 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E369" s="5" t="n">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>439707</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>4393720607861</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4506 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E370" s="5" t="n">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>431369</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>4393720473282</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4506 LED</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E371" s="5" t="n">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>441457</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>4393720610953</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45106 Color Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E372" s="5" t="n">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>432584</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>4393720476603</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45127 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E373" s="5" t="n">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>438302</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>4393720604709</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45128 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" s="5" t="n">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>437565</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>4393720604020</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45128 Inverter Steam Color Touch</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" s="5" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>432585</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>4393720476627</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4527 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E376" s="5" t="n">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>434295</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>4393720600824</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4627 Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E377" s="5" t="n">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>439116</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>4393720606338</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4627 Touch Inverter Steam Black</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E378" s="5" t="n">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>438730</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>4393720605584</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4627 Touch Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E379" s="5" t="n">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>434363</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>4393720601111</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4748 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E380" s="5" t="n">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>441512</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>4393720610472</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 49128 Сolor Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E381" s="5" t="n">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="inlineStr">
+        <is>
+          <t>434684</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>4393720601326</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4926 Direct Drive Inverter</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E382" s="5" t="n">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>425222</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>4393720458517</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4947 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E383" s="5" t="n">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>432266</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>4393720476238</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 58411 Direct Drive Inverter Premium Steam</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" s="5" t="n">
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>440457</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>4393720609421</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 995 Direct Drive Touch Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E385" s="5" t="n">
+        <v>5149</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>421116</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>4393720450382</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 4148 D</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E386" s="5" t="n">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>433622</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>4393720600671</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 46148 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E387" s="5" t="n">
+        <v>5699</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>438586</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>4393720605232</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 4628 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" s="5" t="n">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>438587</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>4393720605249</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 4828 Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D389" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E389" s="5" t="n">
+        <v>5849</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>439108</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>4393720606215</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 61211 D Inverter Steam Champagne</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E390" s="5" t="n">
+        <v>5849</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>434692</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>4393720601418</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 61211 Direct Drive Inverter Premium</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E391" s="5" t="n">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>433781</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>4393720600794</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 61212 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E392" s="5" t="n">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>430648</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>4393720471059</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 6148 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393" s="5" t="n">
+        <v>5599</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>432452</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>4393720476474</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 999 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E394" s="5" t="n">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>438786</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>4393720605799</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 4948 Heat Pump</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" s="5" t="n">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>437531</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>4393720603719</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6108 Heat Pump</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E396" s="5" t="n">
+        <v>5799</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>432450</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>4393720476504</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 998 Heat Pump Full Touch Silver</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E397" s="5" t="n">
+        <v>7949</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>430801</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>4393720472155</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WCD 450 WG NoFrost Inverter</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E398" s="5" t="n">
+        <v>9899</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>439580</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>4393720607267</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WFD 450 Built-in Inverter NoFrost White Glass</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" s="5" t="n">
+        <v>11249</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>439611</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>4393720607489</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WR-092 Defrost White</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E400" s="5" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>440028</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>4393720608585</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1700 DeFrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E401" s="5" t="n">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>433046</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>4393720477563</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 500 Inverter NoFrost White</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E402" s="5" t="n">
+        <v>7649</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>433050</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>4393720477600</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 500 Inverter NoFrost White Glass</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E403" s="5" t="n">
+        <v>8099</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>439593</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>4393720607380</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 550 Built-in NoFrost Inverter White Glass</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="5" t="n">
+        <v>9899</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>439705</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>4393720607878</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 550 Inverter NoFrost Black</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" s="5" t="n">
+        <v>8999</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>431525</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>4393720473985</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 600 X NoFrost Inverter Water Dispenser</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E406" s="5" t="n">
+        <v>8099</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>430193</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>4393720470120</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 692 NFW Inverter Ice Maker</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E407" s="5" t="n">
+        <v>10999</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>443499</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>4681008260069</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 475Plus Touch Black</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E408" s="5" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>443496</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>4681008260038</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 475RP Touch Black</t>
+        </is>
+      </c>
+      <c r="D409" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E409" s="5" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>443498</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>4681008260052</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 475RP Touch White</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E410" s="5" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>443494</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>4681008260014</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 476 Touch Black</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E411" s="5" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>443497</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>4681008260045</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 476 Touch White</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E412" s="5" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="inlineStr">
+        <is>
+          <t>443500</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>4681008260076</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 585RP Touch Black</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E413" s="5" t="n">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>443504</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>4681008260113</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 588 Touch Black</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E414" s="5" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3" t="inlineStr">
+        <is>
+          <t>443505</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>4681008260120</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Электрический полотенцесушитель Weissgauff WTW 588 Touch White</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E415" s="5" t="n">
+        <v>919</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H217"/>
+  <autoFilter ref="A3:H415"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>